--- a/data/output/evaluasi_64.xlsx
+++ b/data/output/evaluasi_64.xlsx
@@ -8,8 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="6400" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="6402" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="6471" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="6471" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="6401" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="6411" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="6403" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6404" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6474" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6405" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="6402" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="6409" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="6472" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,6 +435,2142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>provinsi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-84.18938890243255</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>adhb_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>19.24321816537429</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>adhk_pkrt_q1-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>19.65066497611589</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>adhk_pkrt_q2-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>19.01085400889225</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adhk_pkrt_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-41.94751111679155</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>adhk_pklnprt_q1-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-46.21126997157241</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>adhk_pklnprt_q2-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-50.69836887196499</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>adhk_pklnprt_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>64</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-65.70792834457623</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>adhk_pkp_q1-25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>64</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-58.45536319418261</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>adhk_pkp_q2-25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>64</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-53.06684300061899</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>adhk_pkp_q3-25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>64</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-84.31484332126679</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>adhk_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-15.25669433307529</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q1-25 vs q-to-q_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>64</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>68.28049878274649</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>64</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.38364443046657</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>64</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5077497484964142</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25 vs q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>64</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>17.88812150743851</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>64</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8.747005892929021</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>64</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2.637756721699124</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>64</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-8.880271993473432</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>64</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1.290739109553199</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>64</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4.225977543558824</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>64</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-12.45323841120791</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q1-25 vs y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>64</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-13.06456645031118</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q2-25 vs y-on-y_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>64</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-12.61988525702609</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>64</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>69.61484207798591</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>64</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>89.53101965567133</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>64</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>108.8153238594085</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>64</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>213.0234274872995</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>64</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>92.56726208618031</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>64</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>110.9386641399284</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>64</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.6608980678439538</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>64</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>-2.600182992935175</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25 vs y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>64</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>-3.20639527738501</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>64</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>-12.45323841120791</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q1-25 vs c-to-c_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>64</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-12.76255462592207</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q2-25 vs c-to-c_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>64</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-12.71481489429572</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q3-25 vs c-to-c_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>64</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>69.61484207798591</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>64</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>79.68926315235281</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>64</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>88.88586084754708</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25 vs c-to-c_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>64</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>213.0234274872995</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>64</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>136.089179322662</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>64</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>126.6730299546541</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>64</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.6608980678439538</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>64</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-1.646315094404257</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>64</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-2.183567023688004</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25 vs c-to-c_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>64</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>19.70389643554437</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>64</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>-0.3452598003953459</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25 vs implisit_q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>64</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-41.86071095175448</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>64</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-5.527572868546702</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>64</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-8.426498915271875</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25 vs implisit_q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>64</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-67.39388393748914</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>64</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>26.31858833172355</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>64</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>14.25669188496735</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25 vs implisit_q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>64</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4.768046848528894</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>64</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>20.43226760025719</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q1-25 vs implisit_y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>64</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>21.5095059364845</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q2-25 vs implisit_y-on-y_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>64</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>21.40555730933918</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25 vs implisit_y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>64</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>-41.62195941669983</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>64</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>-45.5877116055116</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>64</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>-49.70974845659173</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>64</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>-65.76481125896846</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>64</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>-57.38960763916899</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q2-25 vs implisit_y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>64</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>-52.10703429684615</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25 vs implisit_y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>7.209326386673507</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>6.557309430454238</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q2-25 vs implisit_y-on-y_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kalimantan Timur</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>6.506065780389636</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25 vs implisit_y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.923794709125925</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>29.03335961445341</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.549380385466977</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.915370690878163</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.50722302675294</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.64224975550805</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.179590558874081</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -438,7 +2582,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>provinsi</t>
+          <t>kabupaten/kota</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -464,113 +2608,113 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64</v>
+        <v>6472</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kalimantan Timur</t>
+          <t>Kota Samarinda</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-17.85089129608495</v>
+        <v>-9.683026153797146</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q2-25</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64</v>
+        <v>6472</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kalimantan Timur</t>
+          <t>Kota Samarinda</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.41002060223579</v>
+        <v>-15.86071175846739</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>64</v>
+        <v>6472</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kalimantan Timur</t>
+          <t>Kota Samarinda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-15.05911382603295</v>
+        <v>0.04314512306599973</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_pi_q2-25</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64</v>
+        <v>6472</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kalimantan Timur</t>
+          <t>Kota Samarinda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6036708308170106</v>
+        <v>1.829804566432077</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -585,7 +2729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,11 +2766,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6402</v>
+        <v>6471</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Kutai Barat</t>
+          <t>Kota Balikpapan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -635,54 +2779,54 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.87548470286859</v>
+        <v>1552619.14676538</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>adhk_pkrt_q1-25_ril vs adhk_pkrt_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6402</v>
+        <v>6471</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Kutai Barat</t>
+          <t>Kota Balikpapan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9.87548470286859</v>
+        <v>1570100.8020897</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>adhk_pkrt_q2-25_ril vs adhk_pkrt_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6402</v>
+        <v>6471</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Kutai Barat</t>
+          <t>Kota Balikpapan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,16 +2835,1864 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3820522856007939</v>
+        <v>559736.37324231</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>adhk_pklnprt_q1-25_ril vs adhk_pklnprt_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>681795.1088879501</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adhk_pklnprt_q2-25_ril vs adhk_pklnprt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7964483.81595201</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>adhk_pkp_q1-25_ril vs adhk_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7734997.415846545</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>adhk_pkp_q2-25_ril vs adhk_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-68.6421615418858</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q1-25_ril vs q-to-q_pkrt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>423.9819520063959</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>21.80646845203336</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q2-25_ril vs q-to-q_pklnprt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>888.3963182648403</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25_ril vs q-to-q_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.881371918238161</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25_ril vs q-to-q_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-25.20868835737144</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25_ril vs q-to-q_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-67.48258781353849</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q1-25_ril vs y-on-y_pkrt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-67.89456057875928</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q2-25_ril vs y-on-y_pkrt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>406.5679684777542</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>477.2692972170628</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25_ril vs y-on-y_pklnprt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1376.596942888528</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>906.8663200668377</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25_ril vs y-on-y_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-23.08669472796793</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-22.14017062476816</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q2-25_ril vs y-on-y_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-67.48258781353849</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q1-25_ril vs c-to-c_pkrt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-67.69104043387379</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q2-25_ril vs c-to-c_pkrt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>406.5679684777542</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>443.0956028900561</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25_ril vs c-to-c_pklnprt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1376.596942888528</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1100.627902720673</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25_ril vs c-to-c_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-23.08669472796793</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-22.62783679772905</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25_ril vs c-to-c_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>226.016867874264</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-79.62321106484625</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-10.55456885340444</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25_ril vs implisit_q-to-q_pklnprt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>-93.233545226686</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>28.07547767447338</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25_ril vs implisit_q-to-q_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>25.12029035278053</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>226.5813871215937</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>229.9899760382976</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q2-25_ril vs implisit_y-on-y_pkrt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>-79.94299883043192</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>-82.27809855577713</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q2-25_ril vs implisit_y-on-y_pklnprt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>-92.9542947815289</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>-91.1722207534071</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q2-25_ril vs implisit_y-on-y_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>25.82204299987171</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>28.89447084189819</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q2-25_ril vs implisit_y-on-y_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-13.03770822452509</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>sog_q_pkrt_q1-25_ril vs sog_q_pkrt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>27.46153143569025</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>sog_q_pkp_q1-25_ril vs sog_q_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.8673721172897616</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>sog_q_pkp_q2-25_ril vs sog_q_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>-13.14343880868692</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pkrt_q1-25_ril vs sog_y-on-y_pkrt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>-13.62674970110016</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pkrt_q2-25_ril vs sog_y-on-y_pkrt_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>28.59170221612237</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pkp_q2-25_ril vs sog_y-on-y_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7890439794382278</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>6.587704574950449</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-5.575811826729565</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-6.675251324434596</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>9.295529093462301</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-67.38309811719419</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>577.7487697459565</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>980.0206448864297</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>-32.57072498331296</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>9.723727821325237</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>-67.58812209870567</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q3-25_prov vs c-to-c_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>486.0881780590307</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1059.515458269469</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>-26.03969012148043</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>-2.370401882790107</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>-17.9028214518203</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>14.9925231032116</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>222.4770352631532</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>-85.08927809984745</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>-90.04360921483769</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>31.11098578455588</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -715,7 +4707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,11 +4744,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6471</v>
+        <v>6401</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Balikpapan</t>
+          <t>Kabupaten Paser</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -765,26 +4757,26 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.001983061351995968</v>
+        <v>15.55483788651773</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6471</v>
+        <v>6401</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Balikpapan</t>
+          <t>Kabupaten Paser</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -793,16 +4785,1692 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.003046834956664407</v>
+        <v>15.55483788651773</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.866724594244834</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25_ril vs c-to-c_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.843423143759459</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>29.3745313465412</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.878155327534074</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9.593123956810912</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.433441344338698</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.015302125601502</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6401</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Paser</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1792521350602005</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.4450571503565</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.214391376890724</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.186872668234623</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>26.69652985492396</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>42.85694805804513</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.813079916189966</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.422712626079766</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>25.68226506752136</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.507494378730424</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.007179607487296275</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.3656704748159698</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.148621709431706</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.4135009056625547</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4169011814617872</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>87.21548013412966</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6403</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>26.25907202768333</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.3642533471107144</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6052673261887451</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.857128439097332</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-41.07979398833939</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-32.34947661153013</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.030233886294425</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3165086461595215</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-7.612404086321871</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6404</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2378767151266422</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.350586728340061</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-13.0574154797698</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.726236134337293</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.209466817577804</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Bontang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1831857386871345</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9427736116923512</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.2382198310645</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-11.71930049675553</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-9.905823124819314</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3853893676584753</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Berau</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1199937323270347</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-15.65534623046696</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7613143206631159</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-13.94206390322678</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.653222016439773</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.942585804798226</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6402</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kutai Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.5828278877849264</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_64.xlsx
+++ b/data/output/evaluasi_64.xlsx
@@ -858,7 +858,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
